--- a/R Markdown/outputs_25_DA/logs_25_DA/verificacao_acoes_2025_25_DA.xlsx
+++ b/R Markdown/outputs_25_DA/logs_25_DA/verificacao_acoes_2025_25_DA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/outputs_25_DA/logs_25_DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_6E87D1D6A9AF53C524D75C17EB3AC75B7F8EC934" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CCC3C77-179E-4611-9257-452A63C496CB}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_6E87D1D6A9AF53C524D75C17EB3AC75B7F8EC934" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46AB372B-010C-4893-B285-6841AA1FE325}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="30180" yWindow="3765" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="referencia_2024" sheetId="1" r:id="rId1"/>
@@ -900,6 +900,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2604,7 +2608,9 @@
   <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="106" customWidth="1"/>
+    <col min="4" max="4" width="50.7109375" customWidth="1"/>
     <col min="6" max="6" width="69.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3859,6 +3865,7 @@
   <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="38.28515625" customWidth="1"/>
     <col min="4" max="4" width="127.140625" customWidth="1"/>
   </cols>
   <sheetData>
